--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Library/AdminApp_Library_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Library/AdminApp_Library_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="305">
   <si>
     <t>S.No.</t>
   </si>
@@ -90,7 +90,7 @@
 6. Every product row shows the product title and a "See materials" link.</t>
   </si>
   <si>
-    <t>Count is environment- and time-specific — assert heading count EQUALS left-nav count, never an absolute number (admin-shared.md §A5). List render measured at ~5.1 s for 970 products on Thor 2026-08-24; budget generously.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Count is environment- and time-specific — assert heading count EQUALS left-nav count, never an absolute number (admin-shared.md §A5). List render measured at ~5.1 s for 970 products on Thor 2026-08-24; budget generously.</t>
   </si>
   <si>
     <t/>
@@ -192,7 +192,7 @@
 2. Uppercase and lowercase initials are interleaved, proving a CASE-INSENSITIVE comparison. A code-point comparison would place every uppercase title before every lowercase one, and "Y Test Product" before "vm_automation_book101".</t>
   </si>
   <si>
-    <t>IMPORTANT CONTRAST: the Classes tab sorts by CODE POINT (admin-shared.md §A4). The Library tab does NOT. Do not reuse the Classes-tab collation expectation here. Verified live 2026-08-24.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. IMPORTANT CONTRAST: the Classes tab sorts by CODE POINT (admin-shared.md §A4). The Library tab does NOT. Do not reuse the Classes-tab collation expectation here. Verified live 2026-08-24.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_6</t>
@@ -212,7 +212,7 @@
     <t>1. After reload the list is back in the default A→Z order — the descending choice is NOT persisted.</t>
   </si>
   <si>
-    <t>Matches the Classes tab, where sorting also does not persist while filter and search do (admin-shared.md §A4). Verified live 2026-08-24.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Matches the Classes tab, where sorting also does not persist while filter and search do (admin-shared.md §A4). Verified live 2026-08-24.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_7</t>
@@ -238,7 +238,7 @@
 3. The result count is unchanged by sorting, and the "Showing search results for vm_automation." banner remains.</t>
   </si>
   <si>
-    <t>Result count is data-dependent — assert that the count is unchanged by sorting, not 22. NOTE: sorting reorders the whole result set alphabetically, which overrides the relevance ranking of TST_LIBR_TC_21. Uses products created by our own automation (vm_automation_*) rather than another team's data, so the expected ranking stays stable as the shared school changes. [user decision, 2026-08-26]</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Result count is data-dependent — assert that the count is unchanged by sorting, not 22. NOTE: sorting reorders the whole result set alphabetically, which overrides the relevance ranking of TST_LIBR_TC_21. Uses products created by our own automation (vm_automation_*) rather than another team's data, so the expected ranking stays stable as the shared school changes. [user decision, 2026-08-26]</t>
   </si>
   <si>
     <t>TST_LIBR_TC_8</t>
@@ -261,7 +261,7 @@
 2. The "Sort by:" label and "Title" control are NOT present in the page — there is nothing to sort.</t>
   </si>
   <si>
-    <t>Genuinely removed from the DOM in this state (verified 2026-08-24), so a presence check is truthful here — unlike most admin dialogs (admin-shared.md §B2).</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Genuinely removed from the DOM in this state (verified 2026-08-24), so a presence check is truthful here — unlike most admin dialogs (admin-shared.md §B2).</t>
   </si>
   <si>
     <t>TST_LIBR_TC_9</t>
@@ -288,7 +288,7 @@
 The list itself did flip (first item "(Do Not Edit) sj11042501" → "yaminitestproduct1"), so sorting works — only the indicator is missing.</t>
   </si>
   <si>
-    <t>STATUS: acknowledged as a VALID concern by the user 2026-08-26 — RECORDED AS A REMARK FOR NOW, deliberately NOT raised as a defect ticket yet. Revisit before the batch is signed off. Two separable halves: (a) the missing visual arrow may be a deliberate design choice; (b) the missing aria-sort is an ACCESSIBILITY gap — a screen-reader user has no way at all to learn the sort direction — and stands on its own regardless of (a). Evidence re-captured live 2026-08-26 by comparing the full outerHTML before and after a click; they are identical. AUTOMATION NOTE: assert list ORDER, never the control's class or text — the control genuinely cannot distinguish the two states.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. STATUS: acknowledged as a VALID concern by the user 2026-08-26 — RECORDED AS A REMARK FOR NOW, deliberately NOT raised as a defect ticket yet. Revisit before the batch is signed off. Two separable halves: (a) the missing visual arrow may be a deliberate design choice; (b) the missing aria-sort is an ACCESSIBILITY gap — a screen-reader user has no way at all to learn the sort direction — and stands on its own regardless of (a). Evidence re-captured live 2026-08-26 by comparing the full outerHTML before and after a click; they are identical. AUTOMATION NOTE: assert list ORDER, never the control's class or text — the control genuinely cannot distinguish the two states.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_10</t>
@@ -392,7 +392,7 @@
 3. The "Search by title" box is emptied.</t>
   </si>
   <si>
-    <t>AUTOMATION NOTE: the Clear link carries qid "aClass-99" — a Classes-tab qid reused on the Library tab. It is NOT a Library qid; do not assume the aLibrary-* family covers it.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. AUTOMATION NOTE: the Clear link carries qid "aClass-99" — a Classes-tab qid reused on the Library tab. It is NOT a Library qid; do not assume the aLibrary-* family covers it.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_14</t>
@@ -414,7 +414,7 @@
 2. Only after Search is clicked does the list narrow and the banner appear.</t>
   </si>
   <si>
-    <t>Search is submit-driven, not live — the same as the Classes tab (admin-shared.md §A4). Verified live 2026-08-24 (970 rows still present after typing).</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Search is submit-driven, not live — the same as the Classes tab (admin-shared.md §A4). Verified live 2026-08-24 (970 rows still present after typing).</t>
   </si>
   <si>
     <t>TST_LIBR_TC_15</t>
@@ -438,7 +438,7 @@
 2. NO "Showing search results for" banner is displayed — an empty term is treated as "no search", not as a search for an empty string.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-24 — 970 rows restored, banner absent.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 — 970 rows restored, banner absent.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_16</t>
@@ -458,7 +458,7 @@
     <t>1. After reload the FULL product list is shown, the heading reads "Library (N)", the search box is empty and no banner is present — the search term is NOT persisted.</t>
   </si>
   <si>
-    <t>IMPORTANT CONTRAST: the Classes tab search DOES persist server-side across reload and login (admin-shared.md §A4). The Library tab does NOT. Verified live 2026-08-24.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. IMPORTANT CONTRAST: the Classes tab search DOES persist server-side across reload and login (admin-shared.md §A4). The Library tab does NOT. Verified live 2026-08-24.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_17</t>
@@ -479,7 +479,7 @@
 2. The "School licence" section is UNCHANGED — the same tiles, in the same order, with the same heading and description. Search applies only to the product list.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-24 (all 3 licence tiles remained while the list narrowed) and re-confirmed with vm_automation 2026-08-26. Uses products created by our own automation (vm_automation_*) rather than another team's data, so the expected ranking stays stable as the shared school changes. [user decision, 2026-08-26]</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 (all 3 licence tiles remained while the list narrowed) and re-confirmed with vm_automation 2026-08-26. Uses products created by our own automation (vm_automation_*) rather than another team's data, so the expected ranking stays stable as the shared school changes. [user decision, 2026-08-26]</t>
   </si>
   <si>
     <t>TST_LIBR_TC_18</t>
@@ -497,7 +497,7 @@
 ACTUAL (Thor, 2026-08-26): the "(N)" count is REMOVED as soon as a search is active. The heading reads "Library" followed only by "Showing search results for vm_automation." and "Clear". The user cannot tell how many products matched without counting the rows.</t>
   </si>
   <si>
-    <t>STATUS: acknowledged as a valid gap by the user 2026-08-26 — RECORDED AS A REMARK FOR NOW, deliberately NOT raised as a defect ticket. Revisit before sign-off alongside TST_LIBR_TC_9. Weaker than TC_9: there is no accessibility dimension here, it is purely a convenience gap — the results are on screen, only the tally is missing. AUTOMATION NOTE: do NOT assert a heading count while a search is active — there is none. Assert the banner text ("Showing search results for &lt;term&gt;.") instead, and count the rendered rows if a number is needed.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. STATUS: acknowledged as a valid gap by the user 2026-08-26 — RECORDED AS A REMARK FOR NOW, deliberately NOT raised as a defect ticket. Revisit before sign-off alongside TST_LIBR_TC_9. Weaker than TC_9: there is no accessibility dimension here, it is purely a convenience gap — the results are on screen, only the tally is missing. AUTOMATION NOTE: do NOT assert a heading count while a search is active — there is none. Assert the banner text ("Showing search results for &lt;term&gt;.") instead, and count the rendered rows if a number is needed.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_19</t>
@@ -520,7 +520,7 @@
 3. The closest match still ranks first — "vm_automation_testing_108" is result 1.</t>
   </si>
   <si>
-    <t>CONFIRMED INTENDED BEHAVIOUR by the product team [2026-08-26] — this is not a defect. Documented here so nobody re-raises it, and so no automation asserts that adding a word narrows the search. Uses products created by our own automation (vm_automation_*) rather than another team's data, so the expected ranking stays stable as the shared school changes. [user decision, 2026-08-26]</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. CONFIRMED INTENDED BEHAVIOUR by the product team [2026-08-26] — this is not a defect. Documented here so nobody re-raises it, and so no automation asserts that adding a word narrows the search. Uses products created by our own automation (vm_automation_*) rather than another team's data, so the expected ranking stays stable as the shared school changes. [user decision, 2026-08-26]</t>
   </si>
   <si>
     <t>TST_LIBR_TC_20</t>
@@ -569,7 +569,7 @@
 3. The search never returns zero results while a substring match exists.</t>
   </si>
   <si>
-    <t>CONFIRMED INTENDED BEHAVIOUR by the product team [2026-08-26] — the search is deliberately fuzzy, so a rough or mistyped term still finds something. Originally written as a defect; RECLASSIFIED from Negative to Edge. AUTOMATION: never assert that every result contains the term — that fails against the live product. Assert the RANKING instead (substring matches first), which held across every term tried on 2026-08-26. Uses products created by our own automation (vm_automation_*) rather than another team's data, so the expected ranking stays stable as the shared school changes. [user decision, 2026-08-26]</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. CONFIRMED INTENDED BEHAVIOUR by the product team [2026-08-26] — the search is deliberately fuzzy, so a rough or mistyped term still finds something. Originally written as a defect; RECLASSIFIED from Negative to Edge. AUTOMATION: never assert that every result contains the term — that fails against the live product. Assert the RANKING instead (substring matches first), which held across every term tried on 2026-08-26. Uses products created by our own automation (vm_automation_*) rather than another team's data, so the expected ranking stays stable as the shared school changes. [user decision, 2026-08-26]</t>
   </si>
   <si>
     <t>TST_LIBR_TC_22</t>
@@ -593,7 +593,7 @@
 ACTUAL (Thor, 2026-08-24) — DEFECT: the term is NOT trimmed. Zero products are returned and the banner renders the raw spaces — "Showing search results for   ." — leaving a visible gap before the full stop and giving the user no readable indication of what was searched.</t>
   </si>
   <si>
-    <t>Low user impact but a clear input-handling gap. The same trimming question applies to leading/trailing spaces around a real term — not yet tested, worth adding once the trimming behaviour is decided.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Low user impact but a clear input-handling gap. The same trimming question applies to leading/trailing spaces around a real term — not yet tested, worth adding once the trimming behaviour is decided.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_23</t>
@@ -648,7 +648,7 @@
 4. The tile shows the product's cover image where the product has one.</t>
   </si>
   <si>
-    <t>Verified live 2026-08-24. The &lt;PLACEHOLDER&gt; for other environments is &lt;IN_DATE_LICENCE_TITLE&gt;.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24. The &lt;PLACEHOLDER&gt; for other environments is &lt;IN_DATE_LICENCE_TITLE&gt;.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_25</t>
@@ -699,7 +699,7 @@
 3. A warning/error icon (error.svg, class "school-licence-icon") is rendered immediately before the date, which the in-date tile does not have.</t>
   </si>
   <si>
-    <t>The icon carries alt="" so its meaning is not exposed to screen-reader users — an accessibility observation worth raising separately. Verified live 2026-08-24.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. The icon carries alt="" so its meaning is not exposed to screen-reader users — an accessibility observation worth raising separately. Verified live 2026-08-24.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_27</t>
@@ -722,7 +722,7 @@
 2. The School licence section is an additional highlight of those products, not a separate inventory — so the products are not double-counted or omitted from "Library (N)".</t>
   </si>
   <si>
-    <t>Verified live 2026-08-24 — all 3 licence titles found among the 970 list rows. ⚠️ IMPORTANT CONTEXT ADDED 2026-08-26: the main product list is CATALOGUE-WIDE, not licence-driven. Perf Test School 4 · key ACJ-DXL-JKR · org slug org_perf_testschool_4 holds ZERO licences and still lists the SAME 970 products as FCN-CHZ-PDA, which holds 3 (see TST_LIBR_TC_30). So a licensed product appearing in the list proves nothing about licensing — the list would contain it either way. Do not read this case as evidence that the list is derived from licences.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 — all 3 licence titles found among the 970 list rows. ⚠️ IMPORTANT CONTEXT ADDED 2026-08-26: the main product list is CATALOGUE-WIDE, not licence-driven. Perf Test School 4 · key ACJ-DXL-JKR · org slug org_perf_testschool_4 holds ZERO licences and still lists the SAME 970 products as FCN-CHZ-PDA, which holds 3 (see TST_LIBR_TC_30). So a licensed product appearing in the list proves nothing about licensing — the list would contain it either way. Do not read this case as evidence that the list is derived from licences.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_28</t>
@@ -746,7 +746,7 @@
 3. The tile's title and date line stay correctly aligned — the layout does not collapse.</t>
   </si>
   <si>
-    <t>The same placeholder is used on rows in the main product list. Verified in the DOM live 2026-08-24; the visual alignment claim is [ASSUMED] — confirm by eye or by a visual snapshot during automation.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. The same placeholder is used on rows in the main product list. Verified in the DOM live 2026-08-24; the visual alignment claim is [ASSUMED] — confirm by eye or by a visual snapshot during automation.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_29</t>
@@ -773,7 +773,7 @@
 4. The date line stays below the title and remains readable.</t>
   </si>
   <si>
-    <t>VERIFIED LIVE 2026-08-26 (previously [ASSUMED] — the word-wrap class had been read from the DOM but the rendering was never measured). Measurements: desktop viewport 1046 px → tile 327 px, title 229 px, 3 lines; narrow viewport 400 px → tile 351 px, title 261 px, 2 lines; overflowsTileRight false and textOverflowsOwnBox false at BOTH widths. ⚠️ SCOPE: this case covers the SCHOOL LICENCE TILE only. The main product-list rows behave DIFFERENTLY and do overflow at narrow widths — see TST_LIBR_TC_31. Do not generalise this result to the list. ⚠️ TITLE CHURN: this product was RENAMED on the shared school between 2026-08-24 and 2026-08-26 (was "testumbrellabundleverylongnametocheckwrappingoftext", now "testumbrellabundlevery_longname_tocheck_wrapping_oftext"). Treat the literal title as &lt;LONG_TITLE_PRODUCT&gt; and re-read it at run time rather than hard-coding it.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. VERIFIED LIVE 2026-08-26 (previously [ASSUMED] — the word-wrap class had been read from the DOM but the rendering was never measured). Measurements: desktop viewport 1046 px → tile 327 px, title 229 px, 3 lines; narrow viewport 400 px → tile 351 px, title 261 px, 2 lines; overflowsTileRight false and textOverflowsOwnBox false at BOTH widths. ⚠️ SCOPE: this case covers the SCHOOL LICENCE TILE only. The main product-list rows behave DIFFERENTLY and do overflow at narrow widths — see TST_LIBR_TC_31. Do not generalise this result to the list. ⚠️ TITLE CHURN: this product was RENAMED on the shared school between 2026-08-24 and 2026-08-26 (was "testumbrellabundleverylongnametocheckwrappingoftext", now "testumbrellabundlevery_longname_tocheck_wrapping_oftext"). Treat the literal title as &lt;LONG_TITLE_PRODUCT&gt; and re-read it at run time rather than hard-coding it.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_30</t>
@@ -801,7 +801,7 @@
 4. The product list is NOT empty — the school still lists the full catalogue (970 products at capture), the same count as a school WITH licences. Holding no licence does not reduce the Library list.</t>
   </si>
   <si>
-    <t>VERIFIED LIVE 2026-08-26 on Perf Test School 4 · key ACJ-DXL-JKR · org slug org_perf_testschool_4 — the school was supplied by the user, who also confirmed the intended behaviour. Previously [ASSUMED] and Blocked; now confirmed and RUNNABLE, so the status is Not Run. DOM evidence: 0 elements matching [qid="sa-lbt-sle-cntr"], 0 .school-licence-container, 0 .school-licence-tile, and the phrase "School licence" absent from document.body.innerText. This is one of the rare places where an ABSENCE check is truthful — the section is genuinely not rendered, not merely hidden (contrast admin-shared.md §B2). ⚠️ AUTOMATION: this case needs a DIFFERENT school from every other case in the batch (ACJ-DXL-JKR, not FCN-CHZ-PDA), so it must set its own school context. Side-effect free.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. VERIFIED LIVE 2026-08-26 on Perf Test School 4 · key ACJ-DXL-JKR · org slug org_perf_testschool_4 — the school was supplied by the user, who also confirmed the intended behaviour. Previously [ASSUMED] and Blocked; now confirmed and RUNNABLE, so the status is Not Run. DOM evidence: 0 elements matching [qid="sa-lbt-sle-cntr"], 0 .school-licence-container, 0 .school-licence-tile, and the phrase "School licence" absent from document.body.innerText. This is one of the rare places where an ABSENCE check is truthful — the section is genuinely not rendered, not merely hidden (contrast admin-shared.md §B2). ⚠️ AUTOMATION: this case needs a DIFFERENT school from every other case in the batch (ACJ-DXL-JKR, not FCN-CHZ-PDA), so it must set its own school context. Side-effect free.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_31</t>
@@ -828,7 +828,7 @@
 ROOT CAUSE (from computed styles): the School licence tile's title sits in "card-title word-wrap" with word-break: break-word, so it wraps. The list row's title (span.item-text) has word-break: normal and only overflow-wrap: break-word, which does NOT break a long unbroken token in this layout. The two are styled inconsistently.</t>
   </si>
   <si>
-    <t>FOUND 2026-08-26 while verifying TST_LIBR_TC_29 — the licence tile wraps correctly, which is what made the list's behaviour stand out. NOT in the source scenario list; added because it is a real rendering defect on the screen under test. Appended as TC_31 rather than inserted, so no existing ID was renumbered (admin-shared.md / manual-test-standard ordering rule). Grouped under scenario #3 because it was found through the School licence comparison; move it if a responsive-layout requirement is added later. Affects narrow desktop windows and mobile widths. Good VISUAL-REGRESSION candidate. Side-effect free.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. FOUND 2026-08-26 while verifying TST_LIBR_TC_29 — the licence tile wraps correctly, which is what made the list's behaviour stand out. NOT in the source scenario list; added because it is a real rendering defect on the screen under test. Appended as TC_31 rather than inserted, so no existing ID was renumbered (admin-shared.md / manual-test-standard ordering rule). Grouped under scenario #3 because it was found through the School licence comparison; move it if a responsive-layout requirement is added later. Affects narrow desktop windows and mobile widths. Good VISUAL-REGRESSION candidate. Side-effect free.</t>
   </si>
   <si>
     <t>TST_UMBP_TC_1</t>
@@ -929,7 +929,7 @@
 4. A "Learning materials" heading and an "Activate materials" control are present.</t>
   </si>
   <si>
-    <t>See TST_UMBP_TC_10 — the "Back" control is present but does NOT return to the Library tab. "Activate materials" is deliberately NOT exercised by this batch (see TST_UMBP_TC_7 Remarks).</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. See TST_UMBP_TC_10 — the "Back" control is present but does NOT return to the Library tab. "Activate materials" is deliberately NOT exercised by this batch (see TST_UMBP_TC_7 Remarks).</t>
   </si>
   <si>
     <t>TST_UMBP_TC_5</t>
@@ -956,7 +956,7 @@
 4. The "Add to Class" button is DISABLED until a class is selected.</t>
   </si>
   <si>
-    <t>SIDE-EFFECT FREE ONLY IF the action is not completed — adding material to a class mutates the shared school, so this case stops at the dialog. TWO OBSERVATIONS: (a) each class row renders as "[&lt;class name&gt;] [&lt;class key&gt;]" with LITERAL square brackets in the text, e.g. "[mn] [acPZ-EQTo]" (raw markup: &lt;button class="dropdown-item work-break class-list"&gt;[mn] [acPZ-EQTo]&lt;/button&gt;). CONFIRMED AS-DESIGNED [user, 2026-08-26] — this is the intended display format, NOT leftover template markup. Recorded for reference so it is not re-flagged as a defect; expected results may assert it verbatim; (b) only 5 classes were VISIBLE although the school shows 106, while 2330 class options sit pre-rendered and hidden behind the dialog — so it is NOT that only 5 exist. [ASSUMED] the visible list is paged/lazily loaded, or filtered (e.g. to the admin's own classes), or intended to be reached via the "Search classes" box rather than scrolled. DECISION [user, 2026-08-26]: reason UNKNOWN and not chased — scrolling and searching the list were avoided because the next click in that dialog adds material to a real class on the shared school, irreversibly. ⚠️ NEVER ASSERT A CLASS COUNT in this dialog, and do not treat "only 5 shown" as a defect. Assert the dialog's structure instead: heading, Search classes input, a non-empty class list, and Add to Class disabled until a selection is made. AUTOMATION TRAP: 2330 pre-rendered class options, ALL sharing the single qid "t-prd-umb-dd-1" and all hidden until the dialog opens — a presence check is a guaranteed false green (admin-shared.md §B2).</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. SIDE-EFFECT FREE ONLY IF the action is not completed — adding material to a class mutates the shared school, so this case stops at the dialog. TWO OBSERVATIONS: (a) each class row renders as "[&lt;class name&gt;] [&lt;class key&gt;]" with LITERAL square brackets in the text, e.g. "[mn] [acPZ-EQTo]" (raw markup: &lt;button class="dropdown-item work-break class-list"&gt;[mn] [acPZ-EQTo]&lt;/button&gt;). CONFIRMED AS-DESIGNED [user, 2026-08-26] — this is the intended display format, NOT leftover template markup. Recorded for reference so it is not re-flagged as a defect; expected results may assert it verbatim; (b) only 5 classes were VISIBLE although the school shows 106, while 2330 class options sit pre-rendered and hidden behind the dialog — so it is NOT that only 5 exist. [ASSUMED] the visible list is paged/lazily loaded, or filtered (e.g. to the admin's own classes), or intended to be reached via the "Search classes" box rather than scrolled. DECISION [user, 2026-08-26]: reason UNKNOWN and not chased — scrolling and searching the list were avoided because the next click in that dialog adds material to a real class on the shared school, irreversibly. ⚠️ NEVER ASSERT A CLASS COUNT in this dialog, and do not treat "only 5 shown" as a defect. Assert the dialog's structure instead: heading, Search classes input, a non-empty class list, and Add to Class disabled until a selection is made. AUTOMATION TRAP: 2330 pre-rendered class options, ALL sharing the single qid "t-prd-umb-dd-1" and all hidden until the dialog opens — a presence check is a guaranteed false green (admin-shared.md §B2).</t>
   </si>
   <si>
     <t>TST_UMBP_TC_6</t>
@@ -978,7 +978,7 @@
 3. No "Activate" control is offered for a component already covered by an active licence.</t>
   </si>
   <si>
-    <t>Copy captured live 2026-08-24. NOTE the different date wording used elsewhere: components on the R55 product show a bare "Expires" + date on its own line with no "Started:", and School licence TILES use "Expires &lt;date&gt;" with no colon (TST_LIBR_TC_24). Three date formats across one feature — worth raising as a consistency issue.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Copy captured live 2026-08-24. NOTE the different date wording used elsewhere: components on the R55 product show a bare "Expires" + date on its own line with no "Started:", and School licence TILES use "Expires &lt;date&gt;" with no colon (TST_LIBR_TC_24). Three date formats across one feature — worth raising as a consistency issue.</t>
   </si>
   <si>
     <t>TST_UMBP_TC_7</t>
@@ -1001,7 +1001,7 @@
 3. "Activate" and "Re-activate" are visually distinct states, not the same label.</t>
   </si>
   <si>
-    <t>DELIBERATELY READ-ONLY. Activation changes the school's entitlement for every teacher and student and cannot be undone on the shared school FCN-CHZ-PDA (admin-shared.md §A5), so this case asserts the CONTROLS and STATUS TEXT only. Exercising activation needs a dedicated school and is out of scope for this batch.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. DELIBERATELY READ-ONLY. Activation changes the school's entitlement for every teacher and student and cannot be undone on the shared school FCN-CHZ-PDA (admin-shared.md §A5), so this case asserts the CONTROLS and STATUS TEXT only. Exercising activation needs a dedicated school and is out of scope for this batch.</t>
   </si>
   <si>
     <t>TST_UMBP_TC_8</t>
@@ -1025,7 +1025,7 @@
 2. The numbers are consistent with the component states shown on the tiles below.</t>
   </si>
   <si>
-    <t>INCONSISTENCY FOUND 2026-08-24, REVIEWED 2026-08-26: the summary is present on "R55 Multi Component Umbrella" but ABSENT on "testumbrellabundlevery_longname_tocheck_wrapping_oftext" — and not because everything there is active: that product has 15 components, several showing Activate or Re-activate (Test1 → Activate; Test Generator → Re-activate/Expired Jul 12 2022; Presentation Plus → Re-activate/Expired Jul 5 2022). So there is plenty to count, yet no line. The RULE governing when the line appears is [ASSUMED] — candidates are product type, component type, or a genuine defect; it cannot be told apart from outside the app. DECISION [user, 2026-08-26]: rule UNKNOWN and not chased for now. This case therefore asserts the summary ONLY on r55multicomponent, where it is verified. ⚠️ DO NOT write an assertion that the line is always present, and do not treat its absence on another product as a defect until the rule is known — that would be a false failure. If the rule is later established, widen this case then.</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. INCONSISTENCY FOUND 2026-08-24, REVIEWED 2026-08-26: the summary is present on "R55 Multi Component Umbrella" but ABSENT on "testumbrellabundlevery_longname_tocheck_wrapping_oftext" — and not because everything there is active: that product has 15 components, several showing Activate or Re-activate (Test1 → Activate; Test Generator → Re-activate/Expired Jul 12 2022; Presentation Plus → Re-activate/Expired Jul 5 2022). So there is plenty to count, yet no line. The RULE governing when the line appears is [ASSUMED] — candidates are product type, component type, or a genuine defect; it cannot be told apart from outside the app. DECISION [user, 2026-08-26]: rule UNKNOWN and not chased for now. This case therefore asserts the summary ONLY on r55multicomponent, where it is verified. ⚠️ DO NOT write an assertion that the line is always present, and do not treat its absence on another product as a defect until the rule is known — that would be a false failure. If the rule is later established, widen this case then.</t>
   </si>
   <si>
     <t>TST_UMBP_TC_9</t>
@@ -1076,7 +1076,31 @@
 ACTUAL (Thor, 2026-08-24) — DEFECT: "Back" requests "/admin/admin//library" — the org slug is MISSING and the path contains a doubled slash. That route does not resolve, and the app redirects to /admin/admin/dashboard ("My school accounts"). The school context is LOST and the admin must re-select the school and re-open the Library tab to continue.</t>
   </si>
   <si>
-    <t>HIGH IMPACT — it breaks the browse loop: every product an admin inspects costs two extra clicks to get back. Reproduced twice on 2026-08-24, once via a scripted click and once via a real user click, on two different products. AUTOMATION NOTE: a suite that opens a product MUST re-navigate via the school card afterwards; it cannot rely on Back (admin-shared.md §A1 — deep-linking the class route fails without school context).</t>
+    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. HIGH IMPACT — it breaks the browse loop: every product an admin inspects costs two extra clicks to get back. Reproduced twice on 2026-08-24, once via a scripted click and once via a real user click, on two different products. AUTOMATION NOTE: a suite that opens a product MUST re-navigate via the school card afterwards; it cannot rely on Back (admin-shared.md §A1 — deep-linking the class route fails without school context).</t>
+  </si>
+  <si>
+    <t>TST_LIBR_TC_33</t>
+  </si>
+  <si>
+    <t>Verify every sortable Library column orders the product list in both directions</t>
+  </si>
+  <si>
+    <t>#1 - Verify Sort feature</t>
+  </si>
+  <si>
+    <t>On the Library tab of a school holding multiple products.</t>
+  </si>
+  <si>
+    <t>1. Identify every sort control the Library tab offers and record them. 2. For each control other than Title, apply it and read the resulting order. 3. Apply it a second time and confirm the order reverses.</t>
+  </si>
+  <si>
+    <t>A school with enough products to make ordering observable.</t>
+  </si>
+  <si>
+    <t>Each sortable column orders the list correctly and reverses on a second click. [ASSUMED] - and the premise itself is unconfirmed.</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_LIB_001, which says "each sortable column header (e.g., Title, Date added)". All eight of our sort cases (TST_LIBR_TC_2-TC_9) are Title-only. GROUND BEFORE WRITING FURTHER: this document's product reference records only a "Sort by Title" control, so "Date added" may not exist on this screen at all. On the next live pass, enumerate the actual sort controls - if Title is the only one, close this case as not applicable and feed the correction back to the other team rather than leaving a phantom gap. Read-only.</t>
   </si>
 </sst>
 </file>
@@ -1470,7 +1494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -3336,6 +3360,50 @@
         <v>24</v>
       </c>
     </row>
+    <row r="43" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
   <dataValidations count="2">
@@ -3347,6 +3415,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>